--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_medianeta_a_2024_maule.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_medianeta_a_2024_maule.xlsx
@@ -114,7 +114,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 15:08</t>
+    <t xml:space="preserve">2026-09-24 01:57</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
